--- a/project_documents/Unit Test Plan.xlsx
+++ b/project_documents/Unit Test Plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\LLM-Evaluation-system\project_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF55779-C20C-4576-ACBF-B358F946DFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2634A167-50CA-4991-853B-8C1A1722C563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{159838AD-6AC4-488A-92A6-A8C72025F8EA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="63">
   <si>
     <t>Sl: No:</t>
   </si>
@@ -153,6 +153,78 @@
   </si>
   <si>
     <t>Relevant reference answer is retrieved</t>
+  </si>
+  <si>
+    <t>Accuracy Agent Evaluation</t>
+  </si>
+  <si>
+    <t>Compare AI response with retrieved reference</t>
+  </si>
+  <si>
+    <t>Reference answer is available</t>
+  </si>
+  <si>
+    <t>Accuracy score generated correctly</t>
+  </si>
+  <si>
+    <t>Relevance Agent Evaluation</t>
+  </si>
+  <si>
+    <t>Evaluate AI response relevance</t>
+  </si>
+  <si>
+    <t>User question and response are available</t>
+  </si>
+  <si>
+    <t>Relevance score generated correctly</t>
+  </si>
+  <si>
+    <t>Hallucination Detection</t>
+  </si>
+  <si>
+    <t>Detect unsupported information in AI response</t>
+  </si>
+  <si>
+    <t>AI response is available</t>
+  </si>
+  <si>
+    <t>Hallucination detected correctly</t>
+  </si>
+  <si>
+    <t>Overall Evaluation Calculation</t>
+  </si>
+  <si>
+    <t>Calculate average evaluation score</t>
+  </si>
+  <si>
+    <t>All three agent scores are generated</t>
+  </si>
+  <si>
+    <t>Overall score displayed correctly</t>
+  </si>
+  <si>
+    <t>Judge Agent Dashboard</t>
+  </si>
+  <si>
+    <t>Display evaluation results in dashboard</t>
+  </si>
+  <si>
+    <t>Backend evaluation completed</t>
+  </si>
+  <si>
+    <t>Dashboard displays all evaluation cards</t>
+  </si>
+  <si>
+    <t>Validation Status Display</t>
+  </si>
+  <si>
+    <t>Verify validation status message</t>
+  </si>
+  <si>
+    <t>Evaluation process completed</t>
+  </si>
+  <si>
+    <t>Validation status displayed successfully</t>
   </si>
 </sst>
 </file>
@@ -222,11 +294,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -579,209 +648,320 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF6EECD-765A-4820-8BE7-905F628D9943}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="24.26953125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.36328125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="23.08984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="26.26953125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.36328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.08984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.26953125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+      <c r="F3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+      <c r="F4" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+      <c r="F6" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
+      <c r="F7" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="25" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="F8" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B13" s="1"/>
+      <c r="F9" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
